--- a/docs/PrivateResume_Manual_Test_Cases.xlsx
+++ b/docs/PrivateResume_Manual_Test_Cases.xlsx
@@ -669,12 +669,28 @@
           <t>Manual test-case template</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="18" t="n"/>
-      <c r="G12" s="18" t="n"/>
-      <c r="H12" s="18" t="n"/>
+      <c r="C12" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>2 manual test cases executed and passed</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
@@ -2787,7 +2803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3726,6 +3742,184 @@
       <c r="Q40" s="23" t="n"/>
       <c r="R40" s="23" t="n"/>
       <c r="S40" s="23" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-MR-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Master_Resume</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PDF Upload</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Upload PDF resume from browser</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Candidate logged in</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sample candidate PDF file</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1. Click 'Upload Master PDF'. 2. Select PDF file. 3. Confirm upload.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>File uploaded, text parsed via PyMuPDF, skills populated in Skills tab</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Local Dev</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>File uploaded, feedback message displayed, skills visible in Skills list</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC-MR-002</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Master_Resume</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>File Validation</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Upload invalid file format (non-PDF)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Candidate logged in</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Sample .png or .txt file</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1. Select non-PDF file in upload dialog.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Upload blocked or rejected with clear user error message</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Local Dev</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>File input restricts to .pdf, backend returns 400 Bad Request error</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11406,7 +11600,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>QA Engineer</t>
@@ -11417,7 +11610,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>Verified in browser</t>
@@ -11495,7 +11687,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>QA Engineer</t>
@@ -11506,7 +11697,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>Verified in browser</t>
@@ -11584,7 +11774,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>QA Engineer</t>
@@ -11595,7 +11784,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>Verified in browser</t>

--- a/docs/PrivateResume_Manual_Test_Cases.xlsx
+++ b/docs/PrivateResume_Manual_Test_Cases.xlsx
@@ -703,12 +703,28 @@
           <t>Manual test-case template</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="18" t="n"/>
-      <c r="G13" s="18" t="n"/>
-      <c r="H13" s="18" t="n"/>
+      <c r="C13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>2 manual test cases executed and passed</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
@@ -3814,7 +3830,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>QA Engineer</t>
@@ -3825,7 +3840,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>Verified in browser</t>
@@ -3903,7 +3917,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>QA Engineer</t>
@@ -3914,7 +3927,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>Verified in browser</t>
@@ -3932,7 +3944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4871,6 +4883,184 @@
       <c r="Q40" s="23" t="n"/>
       <c r="R40" s="23" t="n"/>
       <c r="S40" s="23" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-JOB-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Workspace_Job_Input</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Job Intake</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Submit target job description in Workspace</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Candidate logged in with active master resume</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Company: Stripe, Title: Backend Engineer, Raw JD text</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1. Enter company &amp; role. 2. Paste JD. 3. Click Save &amp; Analyze.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Job record created in database and UI advances to Stage 2 (Analyze JD)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Local Dev</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Job persisted, banner indicates active workflow, navigated to Stage 2</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC-JOB-002</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Workspace_Job_Input</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Submit blank job form</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Candidate logged in</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blank inputs</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1. Click Save &amp; Analyze without entering title or JD.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Form submission blocked with validation message</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Local Dev</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Client and backend validation trigger, preventing invalid persistence</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/PrivateResume_Manual_Test_Cases.xlsx
+++ b/docs/PrivateResume_Manual_Test_Cases.xlsx
@@ -737,12 +737,28 @@
           <t>Manual test-case template</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="18" t="n"/>
-      <c r="H14" s="18" t="n"/>
+      <c r="C14" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>2 manual test cases executed and passed</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
@@ -4955,7 +4971,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>QA Engineer</t>
@@ -4966,7 +4981,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>Verified in browser</t>
@@ -5044,7 +5058,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>QA Engineer</t>
@@ -5055,7 +5068,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>Verified in browser</t>
@@ -5073,7 +5085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6012,6 +6024,184 @@
       <c r="Q40" s="23" t="n"/>
       <c r="R40" s="23" t="n"/>
       <c r="S40" s="23" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-JDA-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>JD_Analysis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Analysis Display</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>View structured job requirements in Stage 2</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Target job saved in Stage 1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Raw JD submitted</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1. Submit job in Stage 1. 2. Observe Stage 2 requirements breakdown.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Categorized chips for Required/Preferred skills, languages, frameworks, responsibilities displayed</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Local Dev</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Stage 2 rendered all technical categories and responsibilities cleanly</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC-JDA-002</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>JD_Analysis</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Re-analysis</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Trigger re-analysis from UI</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Stage 2 active with existing analysis</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1. Click 'Re-analyze JD' button.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Analysis re-triggered through Ollama provider and view refreshed</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Local Dev</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Re-analysis completed and success banner confirmed update</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/PrivateResume_Manual_Test_Cases.xlsx
+++ b/docs/PrivateResume_Manual_Test_Cases.xlsx
@@ -771,12 +771,28 @@
           <t>Manual test-case template</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" s="18" t="n"/>
-      <c r="H15" s="18" t="n"/>
+      <c r="C15" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>1 manual test case executed and passed</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
@@ -789,12 +805,28 @@
           <t>Manual test-case template</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" s="18" t="n"/>
-      <c r="H16" s="18" t="n"/>
+      <c r="C16" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>2 manual test cases executed and passed</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
@@ -6096,7 +6128,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>QA Engineer</t>
@@ -6107,7 +6138,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>Verified in browser</t>
@@ -6185,7 +6215,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>QA Engineer</t>
@@ -6196,7 +6225,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>Verified in browser</t>
@@ -6214,7 +6242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7154,6 +7182,95 @@
       <c r="R40" s="23" t="n"/>
       <c r="S40" s="23" t="n"/>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-MATCH-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Match_Analysis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Match Scoring</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>View Estimated Job Match in Stage 3</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Job analyzed in Stage 2</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Candidate profile evidence</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1. Click 'Proceed to Evidence Match'. 2. Observe score card.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Displays 0-100% Estimated Job Match (explicitly not labeled ATS score)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Local Dev</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Score gauge, matched, weak, missing, and unsupported counts rendered correctly</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7165,7 +7282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8104,6 +8221,184 @@
       <c r="Q40" s="23" t="n"/>
       <c r="R40" s="23" t="n"/>
       <c r="S40" s="23" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-EVI-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Evidence Drawer</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Inspect evidence backing matched skills</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Stage 3 active with match results</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1. View Matched Skills list. 2. Observe evidence citation below skill name.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Skill citations show exact project names (e.g. '↳ Project: API Backend Engine')</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Local Dev</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Evidence citations verify candidate claims against actual projects</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC-EVI-002</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Non-Fabrication</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Verify missing skills warning banner</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Stage 3 active with missing skills</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1. Observe Missing Skills section.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Displays prominent alert stating missing skills are not instructions to invent experience</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Usability / Integrity</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Local Dev</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Non-fabrication banner prominently visible with clear notice</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/PrivateResume_Manual_Test_Cases.xlsx
+++ b/docs/PrivateResume_Manual_Test_Cases.xlsx
@@ -839,12 +839,28 @@
           <t>Manual test-case template</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="18" t="n"/>
-      <c r="G17" s="18" t="n"/>
-      <c r="H17" s="18" t="n"/>
+      <c r="C17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>Completed (2 manual tests passed)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
@@ -857,12 +873,28 @@
           <t>Manual test-case template</t>
         </is>
       </c>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
-      <c r="E18" s="18" t="n"/>
-      <c r="F18" s="18" t="n"/>
-      <c r="G18" s="18" t="n"/>
-      <c r="H18" s="18" t="n"/>
+      <c r="C18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>Completed (1 manual test passed)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
@@ -875,12 +907,28 @@
           <t>Manual test-case template</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" s="18" t="n"/>
-      <c r="H19" s="18" t="n"/>
+      <c r="C19" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>Completed (2 manual tests passed)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
@@ -7253,7 +7301,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>QA Engineer</t>
@@ -7264,7 +7311,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>Verified in browser</t>
@@ -8293,7 +8339,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>QA Engineer</t>
@@ -8304,7 +8349,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>Verified in browser</t>
@@ -8382,7 +8426,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>QA Engineer</t>
@@ -8393,7 +8436,6 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>Verified in browser</t>
@@ -8411,7 +8453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9351,6 +9393,316 @@
       <c r="R40" s="23" t="n"/>
       <c r="S40" s="23" t="n"/>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-TAILOR-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Tailored_Resume</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tailored Resume Generation</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Generate v1 resume draft for target job from workspace</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Job added and analyzed in Stages 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Navigate to Stage 4 and click 'Generate Tailored Resume (Draft v1)'</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Target Job: Lead Developer</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Draft v1 is generated with summary, skills, experience, and projects populated</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Draft v1 displayed in Workspace Stage 4 with all sections editable</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC-TAILOR-002</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Tailored_Resume</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Non-Fabrication Rule</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Verify missing skills are excluded from generated resume</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Job description contains skills candidate does not have</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Inspect Skills section in tailored draft</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Candidate skills vs Job skills</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Missing skills identified in Stage 3 are NOT added to the resume</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Missing skills absent from generated resume; only genuine skills present</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TC-TAILOR-001</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Tailored_Resume</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tailored Resume Generation</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Generate v1 resume draft for target job from workspace</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Job added and analyzed in Stages 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Navigate to Stage 4 and click 'Generate Tailored Resume (Draft v1)'</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Target Job: Lead Developer</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Draft v1 is generated with summary, skills, experience, and projects populated</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Draft v1 displayed in Workspace Stage 4 with all sections editable</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TC-TAILOR-002</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Tailored_Resume</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Non-Fabrication Rule</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Verify missing skills are excluded from generated resume</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Job description contains skills candidate does not have</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Inspect Skills section in tailored draft</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Candidate skills vs Job skills</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Missing skills identified in Stage 3 are NOT added to the resume</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Missing skills absent from generated resume; only genuine skills present</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9362,7 +9714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10302,6 +10654,161 @@
       <c r="R40" s="23" t="n"/>
       <c r="S40" s="23" t="n"/>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-AIEDIT-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AI_Editing</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ask AI Section Revision</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Refine summary and experience bullets with AI consultation modal</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Tailored resume draft loaded in Stage 4</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Click 'Ask AI' button, select prompt pill, and click Generate</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Prompt: 'Emphasize measurable outcomes and technical metrics'</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>AI returns proposed revision with clear rationale</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Proposed revision displayed side-by-side; clicking Accept updates the resume section</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC-AIEDIT-001</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AI_Editing</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ask AI Section Revision</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Refine summary and experience bullets with AI consultation modal</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Tailored resume draft loaded in Stage 4</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Click 'Ask AI' button, select prompt pill, and click Generate</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Prompt: 'Emphasize measurable outcomes and technical metrics'</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>AI returns proposed revision with clear rationale</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Proposed revision displayed side-by-side; clicking Accept updates the resume section</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10313,7 +10820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11252,6 +11759,316 @@
       <c r="Q40" s="23" t="n"/>
       <c r="R40" s="23" t="n"/>
       <c r="S40" s="23" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-VER-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Versioning</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Save as New Version</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Create v2 snapshot from edited draft</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Draft v1 edited in Stage 4</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Click 'Save as New Version (v2)'</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Modified summary &amp; role title</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>New version v2 is created; version dropdown shows v1 and v2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>v2 created successfully; switching between v1 and v2 in dropdown preserves respective content</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC-VER-002</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Versioning</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Lock as Final</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Mark approved resume version as Final</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Version v2 reviewed and ready</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Click 'Lock as Final'</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Version v2</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Status badge transitions to green FINAL pill; in-place editing locked</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Status updated to FINAL; subsequent edits automatically create new draft version v3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TC-VER-001</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Versioning</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Save as New Version</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Create v2 snapshot from edited draft</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Draft v1 edited in Stage 4</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Click 'Save as New Version (v2)'</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Modified summary &amp; role title</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>New version v2 is created; version dropdown shows v1 and v2</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>v2 created successfully; switching between v1 and v2 in dropdown preserves respective content</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TC-VER-002</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Versioning</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Lock as Final</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Mark approved resume version as Final</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Version v2 reviewed and ready</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Click 'Lock as Final'</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Version v2</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Status badge transitions to green FINAL pill; in-place editing locked</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Status updated to FINAL; subsequent edits automatically create new draft version v3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/PrivateResume_Manual_Test_Cases.xlsx
+++ b/docs/PrivateResume_Manual_Test_Cases.xlsx
@@ -941,12 +941,28 @@
           <t>Manual test-case template</t>
         </is>
       </c>
-      <c r="C20" s="18" t="n"/>
-      <c r="D20" s="18" t="n"/>
-      <c r="E20" s="18" t="n"/>
-      <c r="F20" s="18" t="n"/>
-      <c r="G20" s="18" t="n"/>
-      <c r="H20" s="18" t="n"/>
+      <c r="C20" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>Completed (2 manual tests passed)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
@@ -9598,7 +9614,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>Manual / UI</t>
@@ -9676,7 +9691,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>Manual / UI</t>
@@ -10782,7 +10796,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>Manual / UI</t>
@@ -11965,7 +11978,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>Manual / UI</t>
@@ -12043,7 +12055,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>Manual / UI</t>
@@ -13293,7 +13304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14232,6 +14243,162 @@
       <c r="Q40" s="23" t="n"/>
       <c r="R40" s="23" t="n"/>
       <c r="S40" s="23" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-PDF-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PDF_Generation</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ATS Resume Compilation</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Compile tailored resume into PDF from Workspace Stage 5</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Tailored resume active in Stage 4/5</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Click 'Compile ATS-Ready PDF'</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Active tailored resume v1</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Document compiles via local MiKTeX pdflatex; inline iframe renders PDF preview</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>PDF compiled cleanly and displayed inline in Stage 5 preview iframe</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC-PDF-002</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PDF_Generation</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Download Artifacts</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Download compiled PDF and LaTeX source files</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Compiled PDF preview available in Stage 5</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Click 'Download PDF' and 'LaTeX Source' buttons</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Resume_Stripe Platforms.pdf and resume_source.tex</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Browser initiates direct download with correct filenames and binary content</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Files downloaded and verified locally in PDF viewer</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/PrivateResume_Manual_Test_Cases.xlsx
+++ b/docs/PrivateResume_Manual_Test_Cases.xlsx
@@ -14295,7 +14295,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>Manual / UI</t>
@@ -14373,7 +14372,6 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>Manual / UI</t>
@@ -14411,7 +14409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15350,6 +15348,160 @@
       <c r="Q40" s="23" t="n"/>
       <c r="R40" s="23" t="n"/>
       <c r="S40" s="23" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-VAL-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ATS Pre-Flight Quality Gate UI</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Display 6-point ATS checklist with badges and score in Workspace Stage 5</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Tailored resume compiled into PDF in Stage 5</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tailored resume v1 PDF</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>View Stage 5 ATS Pre-Flight Quality Gate panel</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Quality Gate panel renders 6 cards with icons (Pass/Warn/Fail), score badge (e.g. 100/100 PASS), and resolution hints</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Stage 5 Quality Gate panel clearly displays all 6 checks with green checkmarks and 100/100 PASS badge</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC-VAL-002</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Re-Run ATS Audit Action</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Trigger validation on-demand using Re-Run ATS Audit button</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Compiled resume in Stage 5</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Click Re-Run ATS Audit</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Click action button</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Audits resume and updates checklist dynamically</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Audit completes and success notification displays with score</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/PrivateResume_Manual_Test_Cases.xlsx
+++ b/docs/PrivateResume_Manual_Test_Cases.xlsx
@@ -15514,7 +15514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16453,6 +16453,160 @@
       <c r="Q40" s="23" t="n"/>
       <c r="R40" s="23" t="n"/>
       <c r="S40" s="23" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-APP-001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Application Pipeline UI</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>View tracked applications, filter by status, update stages, and edit notes</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>User with logged application</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Open Applications tab</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Filter tabs, change status dropdown, write and save notes</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Status updates immediately; notes persisted; PDF download link available</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Application pipeline renders cleanly, status transitions update database, notes persist</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC-APP-002</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1-Click Workspace Logging</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Log application directly from Workspace Stage 5 after PDF compilation</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Tailored resume compiled into PDF in Stage 5</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Click "Log Application" button in Stage 5 toolbar</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Button clicked in Stage 5</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Creates application in pipeline and shows success confirmation toast</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Application logged successfully and appeared in Applications tab</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Manual / UI</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Verified in browser</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/PrivateResume_Manual_Test_Cases.xlsx
+++ b/docs/PrivateResume_Manual_Test_Cases.xlsx
@@ -975,12 +975,28 @@
           <t>Manual test-case template</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="18" t="n"/>
-      <c r="G21" s="18" t="n"/>
-      <c r="H21" s="18" t="n"/>
+      <c r="C21" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>Completed (2 manual UI tests passed: Quality gate card &amp; on-demand audit)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
@@ -993,12 +1009,28 @@
           <t>Manual test-case template</t>
         </is>
       </c>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" s="18" t="n"/>
-      <c r="H22" s="18" t="n"/>
+      <c r="C22" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>Completed (2 manual UI tests passed: Pipeline tracker &amp; 1-click workspace logging)</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
@@ -1011,12 +1043,28 @@
           <t>Manual test-case template</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
+      <c r="C23" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="18" t="inlineStr">
+        <is>
+          <t>Completed (Playwright E2E browser candidate journeys verified)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
